--- a/Dash.xlsx
+++ b/Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ouvidor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172FC04C-6F20-49A4-A12F-26D6DB410B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C74626-1C27-40E5-8B80-C8051720CD7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{B202361E-0C35-4463-8CF9-A9C2146372B9}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Dash" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$238</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$247</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="119">
   <si>
     <t>Protocolo</t>
   </si>
@@ -382,6 +382,9 @@
   </si>
   <si>
     <t>Assuntos Diversos</t>
+  </si>
+  <si>
+    <t>Poluentes industriais/ serviços</t>
   </si>
 </sst>
 </file>
@@ -925,7 +928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}">
-  <dimension ref="A1:J238"/>
+  <dimension ref="A1:J247"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.85546875" customWidth="1"/>
@@ -8078,7 +8081,9 @@
       <c r="G217" s="6">
         <v>46233</v>
       </c>
-      <c r="H217" s="27"/>
+      <c r="H217" s="28">
+        <v>46279</v>
+      </c>
       <c r="I217" s="14"/>
       <c r="J217" s="20" t="s">
         <v>94</v>
@@ -8110,7 +8115,7 @@
         <v>46240</v>
       </c>
       <c r="I218" s="12" t="str">
-        <f t="shared" ref="I218:I229" si="12">IF(H218&lt;=G218,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" ref="I218:I239" si="12">IF(H218&lt;=G218,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Fora do Prazo</v>
       </c>
       <c r="J218" s="2" t="s">
@@ -8502,10 +8507,15 @@
       <c r="G230" s="7">
         <v>46275</v>
       </c>
-      <c r="H230" s="34"/>
-      <c r="I230" s="14"/>
+      <c r="H230" s="28">
+        <v>46279</v>
+      </c>
+      <c r="I230" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Fora do Prazo</v>
+      </c>
       <c r="J230" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="231" spans="1:10" s="35" customFormat="1" x14ac:dyDescent="0.25">
@@ -8530,10 +8540,15 @@
       <c r="G231" s="6">
         <v>46275</v>
       </c>
-      <c r="H231" s="27"/>
-      <c r="I231" s="14"/>
+      <c r="H231" s="28">
+        <v>46265</v>
+      </c>
+      <c r="I231" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J231" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="232" spans="1:10" s="35" customFormat="1" x14ac:dyDescent="0.25">
@@ -8558,10 +8573,15 @@
       <c r="G232" s="7">
         <v>46275</v>
       </c>
-      <c r="H232" s="34"/>
-      <c r="I232" s="14"/>
+      <c r="H232" s="16">
+        <v>46281</v>
+      </c>
+      <c r="I232" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Fora do Prazo</v>
+      </c>
       <c r="J232" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="233" spans="1:10" s="35" customFormat="1" x14ac:dyDescent="0.25">
@@ -8586,10 +8606,15 @@
       <c r="G233" s="6">
         <v>46275</v>
       </c>
-      <c r="H233" s="14"/>
-      <c r="I233" s="14"/>
+      <c r="H233" s="28">
+        <v>46265</v>
+      </c>
+      <c r="I233" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J233" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="234" spans="1:10" s="35" customFormat="1" x14ac:dyDescent="0.25">
@@ -8614,10 +8639,15 @@
       <c r="G234" s="7">
         <v>46278</v>
       </c>
-      <c r="H234" s="34"/>
-      <c r="I234" s="14"/>
+      <c r="H234" s="16">
+        <v>46281</v>
+      </c>
+      <c r="I234" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Fora do Prazo</v>
+      </c>
       <c r="J234" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="235" spans="1:10" s="35" customFormat="1" x14ac:dyDescent="0.25">
@@ -8642,10 +8672,15 @@
       <c r="G235" s="6">
         <v>46281</v>
       </c>
-      <c r="H235" s="14"/>
-      <c r="I235" s="14"/>
+      <c r="H235" s="16">
+        <v>46287</v>
+      </c>
+      <c r="I235" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Fora do Prazo</v>
+      </c>
       <c r="J235" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="236" spans="1:10" s="35" customFormat="1" x14ac:dyDescent="0.25">
@@ -8670,10 +8705,15 @@
       <c r="G236" s="7">
         <v>46281</v>
       </c>
-      <c r="H236" s="34"/>
-      <c r="I236" s="14"/>
+      <c r="H236" s="16">
+        <v>46262</v>
+      </c>
+      <c r="I236" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J236" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="237" spans="1:10" s="35" customFormat="1" x14ac:dyDescent="0.25">
@@ -8698,10 +8738,15 @@
       <c r="G237" s="6">
         <v>46283</v>
       </c>
-      <c r="H237" s="14"/>
-      <c r="I237" s="14"/>
+      <c r="H237" s="28">
+        <v>46265</v>
+      </c>
+      <c r="I237" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J237" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="238" spans="1:10" s="35" customFormat="1" x14ac:dyDescent="0.25">
@@ -8726,14 +8771,276 @@
       <c r="G238" s="7">
         <v>46285</v>
       </c>
-      <c r="H238" s="34"/>
-      <c r="I238" s="14"/>
+      <c r="H238" s="16">
+        <v>46262</v>
+      </c>
+      <c r="I238" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J238" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A239" s="18">
+        <v>202608007000253</v>
+      </c>
+      <c r="B239" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C239" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D239" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E239" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F239" s="15">
+        <v>46261.773611111108</v>
+      </c>
+      <c r="G239" s="7">
+        <v>46291</v>
+      </c>
+      <c r="H239" s="28">
+        <v>46279</v>
+      </c>
+      <c r="I239" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J239" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A240" s="17">
+        <v>202609007000254</v>
+      </c>
+      <c r="B240" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C240" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D240" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E240" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F240" s="13">
+        <v>46273.647222222222</v>
+      </c>
+      <c r="G240" s="6">
+        <v>46303</v>
+      </c>
+      <c r="H240" s="27"/>
+      <c r="I240" s="14"/>
+      <c r="J240" s="2" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A241" s="18">
+        <v>202609007000255</v>
+      </c>
+      <c r="B241" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C241" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D241" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E241" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F241" s="15">
+        <v>46280.388194444444</v>
+      </c>
+      <c r="G241" s="7">
+        <v>46310</v>
+      </c>
+      <c r="H241" s="34"/>
+      <c r="I241" s="14"/>
+      <c r="J241" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A242" s="17">
+        <v>202609003000256</v>
+      </c>
+      <c r="B242" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C242" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D242" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="E242" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F242" s="13">
+        <v>46286.429861111108</v>
+      </c>
+      <c r="G242" s="6">
+        <v>46316</v>
+      </c>
+      <c r="H242" s="27"/>
+      <c r="I242" s="14"/>
+      <c r="J242" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A243" s="18">
+        <v>202609011000257</v>
+      </c>
+      <c r="B243" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C243" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D243" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E243" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F243" s="15">
+        <v>46286.447916666664</v>
+      </c>
+      <c r="G243" s="7">
+        <v>46316</v>
+      </c>
+      <c r="H243" s="34"/>
+      <c r="I243" s="14"/>
+      <c r="J243" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A244" s="17">
+        <v>202609001000258</v>
+      </c>
+      <c r="B244" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C244" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D244" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E244" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F244" s="13">
+        <v>46286.45208333333</v>
+      </c>
+      <c r="G244" s="6">
+        <v>46316</v>
+      </c>
+      <c r="H244" s="27"/>
+      <c r="I244" s="14"/>
+      <c r="J244" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A245" s="18">
+        <v>202609006000259</v>
+      </c>
+      <c r="B245" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C245" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D245" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E245" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F245" s="15">
+        <v>46286.458333333336</v>
+      </c>
+      <c r="G245" s="7">
+        <v>46316</v>
+      </c>
+      <c r="H245" s="34"/>
+      <c r="I245" s="14"/>
+      <c r="J245" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A246" s="17">
+        <v>202609001000260</v>
+      </c>
+      <c r="B246" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C246" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D246" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E246" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F246" s="13">
+        <v>46287.552777777775</v>
+      </c>
+      <c r="G246" s="6">
+        <v>46317</v>
+      </c>
+      <c r="H246" s="27"/>
+      <c r="I246" s="14"/>
+      <c r="J246" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A247" s="18">
+        <v>202609010000261</v>
+      </c>
+      <c r="B247" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C247" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D247" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E247" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F247" s="15">
+        <v>46288.352083333331</v>
+      </c>
+      <c r="G247" s="7">
+        <v>46318</v>
+      </c>
+      <c r="H247" s="34"/>
+      <c r="I247" s="14"/>
+      <c r="J247" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J238" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
+  <autoFilter ref="A1:J247" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J159">
     <sortCondition ref="F1:F159"/>
   </sortState>

--- a/Dash.xlsx
+++ b/Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ouvidor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C74626-1C27-40E5-8B80-C8051720CD7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03FCBBCB-E3E6-4B11-9C49-113533A74EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{B202361E-0C35-4463-8CF9-A9C2146372B9}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="122">
   <si>
     <t>Protocolo</t>
   </si>
@@ -385,6 +385,15 @@
   </si>
   <si>
     <t>Poluentes industriais/ serviços</t>
+  </si>
+  <si>
+    <t>Comunicação</t>
+  </si>
+  <si>
+    <t>Assessoria de imprensa</t>
+  </si>
+  <si>
+    <t>Calçadas área-privada</t>
   </si>
 </sst>
 </file>
@@ -928,7 +937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}">
-  <dimension ref="A1:J247"/>
+  <dimension ref="A1:J257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.85546875" customWidth="1"/>
@@ -8115,7 +8124,7 @@
         <v>46240</v>
       </c>
       <c r="I218" s="12" t="str">
-        <f t="shared" ref="I218:I239" si="12">IF(H218&lt;=G218,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" ref="I218:I252" si="12">IF(H218&lt;=G218,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Fora do Prazo</v>
       </c>
       <c r="J218" s="2" t="s">
@@ -8837,10 +8846,15 @@
       <c r="G240" s="6">
         <v>46303</v>
       </c>
-      <c r="H240" s="27"/>
-      <c r="I240" s="14"/>
+      <c r="H240" s="28">
+        <v>46295</v>
+      </c>
+      <c r="I240" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J240" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.25">
@@ -8865,10 +8879,15 @@
       <c r="G241" s="7">
         <v>46310</v>
       </c>
-      <c r="H241" s="34"/>
-      <c r="I241" s="14"/>
+      <c r="H241" s="28">
+        <v>46295</v>
+      </c>
+      <c r="I241" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J241" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.25">
@@ -8893,10 +8912,15 @@
       <c r="G242" s="6">
         <v>46316</v>
       </c>
-      <c r="H242" s="27"/>
-      <c r="I242" s="14"/>
+      <c r="H242" s="28">
+        <v>46295</v>
+      </c>
+      <c r="I242" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J242" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.25">
@@ -8949,10 +8973,15 @@
       <c r="G244" s="6">
         <v>46316</v>
       </c>
-      <c r="H244" s="27"/>
-      <c r="I244" s="14"/>
+      <c r="H244" s="28">
+        <v>46295</v>
+      </c>
+      <c r="I244" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J244" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
@@ -8977,10 +9006,15 @@
       <c r="G245" s="7">
         <v>46316</v>
       </c>
-      <c r="H245" s="34"/>
-      <c r="I245" s="14"/>
+      <c r="H245" s="28">
+        <v>46295</v>
+      </c>
+      <c r="I245" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J245" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.25">
@@ -9033,9 +9067,314 @@
       <c r="G247" s="7">
         <v>46318</v>
       </c>
-      <c r="H247" s="34"/>
-      <c r="I247" s="14"/>
+      <c r="H247" s="28">
+        <v>46295</v>
+      </c>
+      <c r="I247" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J247" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A248" s="17">
+        <v>202609009000262</v>
+      </c>
+      <c r="B248" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C248" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D248" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E248" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F248" s="13">
+        <v>46289.399305555555</v>
+      </c>
+      <c r="G248" s="6">
+        <v>46319</v>
+      </c>
+      <c r="H248" s="28">
+        <v>46295</v>
+      </c>
+      <c r="I248" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J248" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A249" s="18">
+        <v>202609007000263</v>
+      </c>
+      <c r="B249" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C249" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D249" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E249" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F249" s="15">
+        <v>46289.404166666667</v>
+      </c>
+      <c r="G249" s="7">
+        <v>46319</v>
+      </c>
+      <c r="H249" s="34"/>
+      <c r="I249" s="14"/>
+      <c r="J249" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A250" s="17">
+        <v>202609015000264</v>
+      </c>
+      <c r="B250" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C250" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D250" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E250" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F250" s="13">
+        <v>46294.487500000003</v>
+      </c>
+      <c r="G250" s="6">
+        <v>46324</v>
+      </c>
+      <c r="H250" s="28">
+        <v>46295</v>
+      </c>
+      <c r="I250" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J250" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A251" s="18">
+        <v>202609011000265</v>
+      </c>
+      <c r="B251" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C251" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D251" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E251" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F251" s="15">
+        <v>46294.495833333334</v>
+      </c>
+      <c r="G251" s="7">
+        <v>46324</v>
+      </c>
+      <c r="H251" s="28">
+        <v>46295</v>
+      </c>
+      <c r="I251" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J251" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A252" s="17">
+        <v>202609007000266</v>
+      </c>
+      <c r="B252" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C252" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="D252" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E252" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F252" s="13">
+        <v>46294.5</v>
+      </c>
+      <c r="G252" s="6">
+        <v>46324</v>
+      </c>
+      <c r="H252" s="28">
+        <v>46295</v>
+      </c>
+      <c r="I252" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J252" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A253" s="18">
+        <v>202609013000267</v>
+      </c>
+      <c r="B253" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C253" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D253" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E253" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F253" s="15">
+        <v>46295.504166666666</v>
+      </c>
+      <c r="G253" s="7">
+        <v>46325</v>
+      </c>
+      <c r="H253" s="14"/>
+      <c r="I253" s="14"/>
+      <c r="J253" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A254" s="17">
+        <v>202609013000268</v>
+      </c>
+      <c r="B254" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C254" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D254" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E254" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F254" s="13">
+        <v>46295.506249999999</v>
+      </c>
+      <c r="G254" s="6">
+        <v>46325</v>
+      </c>
+      <c r="H254" s="14"/>
+      <c r="I254" s="14"/>
+      <c r="J254" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A255" s="18">
+        <v>202609013000269</v>
+      </c>
+      <c r="B255" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C255" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D255" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E255" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F255" s="15">
+        <v>46295.509027777778</v>
+      </c>
+      <c r="G255" s="7">
+        <v>46325</v>
+      </c>
+      <c r="H255" s="34"/>
+      <c r="I255" s="14"/>
+      <c r="J255" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A256" s="17">
+        <v>202610007000270</v>
+      </c>
+      <c r="B256" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C256" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D256" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E256" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F256" s="13">
+        <v>46297.640972222223</v>
+      </c>
+      <c r="G256" s="6">
+        <v>46327</v>
+      </c>
+      <c r="H256" s="27"/>
+      <c r="I256" s="14"/>
+      <c r="J256" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A257" s="18">
+        <v>202610007000271</v>
+      </c>
+      <c r="B257" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C257" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D257" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E257" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F257" s="15">
+        <v>46300.638888888891</v>
+      </c>
+      <c r="G257" s="7">
+        <v>46330</v>
+      </c>
+      <c r="H257" s="14"/>
+      <c r="I257" s="14"/>
+      <c r="J257" s="2" t="s">
         <v>15</v>
       </c>
     </row>

--- a/Dash.xlsx
+++ b/Dash.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ouvidor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03FCBBCB-E3E6-4B11-9C49-113533A74EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F1973C-4D0F-49B2-B79A-B1CCD386C3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{B202361E-0C35-4463-8CF9-A9C2146372B9}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Dash" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$247</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dash!$A$1:$J$265</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="122">
   <si>
     <t>Protocolo</t>
   </si>
@@ -937,7 +937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}">
-  <dimension ref="A1:J257"/>
+  <dimension ref="A1:J265"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.85546875" customWidth="1"/>
@@ -7302,7 +7302,7 @@
         <v>46167</v>
       </c>
       <c r="I193" s="12" t="str">
-        <f t="shared" ref="I193:I216" si="11">IF(H193&lt;=G193,"Dentro do Prazo","Fora do Prazo")</f>
+        <f t="shared" ref="I193:I217" si="11">IF(H193&lt;=G193,"Dentro do Prazo","Fora do Prazo")</f>
         <v>Dentro do Prazo</v>
       </c>
       <c r="J193" s="2" t="s">
@@ -8093,9 +8093,12 @@
       <c r="H217" s="28">
         <v>46279</v>
       </c>
-      <c r="I217" s="14"/>
-      <c r="J217" s="20" t="s">
-        <v>94</v>
+      <c r="I217" s="12" t="str">
+        <f t="shared" si="11"/>
+        <v>Fora do Prazo</v>
+      </c>
+      <c r="J217" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.25">
@@ -8945,10 +8948,15 @@
       <c r="G243" s="7">
         <v>46316</v>
       </c>
-      <c r="H243" s="34"/>
-      <c r="I243" s="14"/>
+      <c r="H243" s="28">
+        <v>46318</v>
+      </c>
+      <c r="I243" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Fora do Prazo</v>
+      </c>
       <c r="J243" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.25">
@@ -9039,10 +9047,15 @@
       <c r="G246" s="6">
         <v>46317</v>
       </c>
-      <c r="H246" s="27"/>
-      <c r="I246" s="14"/>
+      <c r="H246" s="28">
+        <v>46318</v>
+      </c>
+      <c r="I246" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Fora do Prazo</v>
+      </c>
       <c r="J246" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.25">
@@ -9133,10 +9146,15 @@
       <c r="G249" s="7">
         <v>46319</v>
       </c>
-      <c r="H249" s="34"/>
-      <c r="I249" s="14"/>
+      <c r="H249" s="28">
+        <v>46318</v>
+      </c>
+      <c r="I249" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J249" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
@@ -9344,10 +9362,15 @@
       <c r="G256" s="6">
         <v>46327</v>
       </c>
-      <c r="H256" s="27"/>
-      <c r="I256" s="14"/>
+      <c r="H256" s="28">
+        <v>46314</v>
+      </c>
+      <c r="I256" s="12" t="str">
+        <f t="shared" ref="I256:I257" si="13">IF(H256&lt;=G256,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J256" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.25">
@@ -9372,14 +9395,248 @@
       <c r="G257" s="7">
         <v>46330</v>
       </c>
-      <c r="H257" s="14"/>
-      <c r="I257" s="14"/>
+      <c r="H257" s="28">
+        <v>46314</v>
+      </c>
+      <c r="I257" s="12" t="str">
+        <f t="shared" si="13"/>
+        <v>Dentro do Prazo</v>
+      </c>
       <c r="J257" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A258" s="17">
+        <v>202610007000272</v>
+      </c>
+      <c r="B258" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C258" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D258" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E258" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F258" s="13">
+        <v>46303.657638888886</v>
+      </c>
+      <c r="G258" s="6">
+        <v>46333</v>
+      </c>
+      <c r="H258" s="27"/>
+      <c r="I258" s="14"/>
+      <c r="J258" s="2" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A259" s="18">
+        <v>202610007000273</v>
+      </c>
+      <c r="B259" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C259" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D259" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E259" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F259" s="15">
+        <v>46303.870138888888</v>
+      </c>
+      <c r="G259" s="7">
+        <v>46333</v>
+      </c>
+      <c r="H259" s="14"/>
+      <c r="I259" s="14"/>
+      <c r="J259" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A260" s="17">
+        <v>202610015000274</v>
+      </c>
+      <c r="B260" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C260" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D260" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E260" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F260" s="13">
+        <v>46314.746527777781</v>
+      </c>
+      <c r="G260" s="6">
+        <v>46344</v>
+      </c>
+      <c r="H260" s="28">
+        <v>46317</v>
+      </c>
+      <c r="I260" s="12" t="str">
+        <f t="shared" ref="I260" si="14">IF(H260&lt;=G260,"Dentro do Prazo","Fora do Prazo")</f>
+        <v>Dentro do Prazo</v>
+      </c>
+      <c r="J260" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A261" s="18">
+        <v>202610007000275</v>
+      </c>
+      <c r="B261" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C261" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D261" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E261" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F261" s="15">
+        <v>46315.478472222225</v>
+      </c>
+      <c r="G261" s="7">
+        <v>46345</v>
+      </c>
+      <c r="H261" s="34"/>
+      <c r="I261" s="14"/>
+      <c r="J261" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A262" s="17">
+        <v>202610007000276</v>
+      </c>
+      <c r="B262" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C262" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D262" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E262" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F262" s="13">
+        <v>46315.844444444447</v>
+      </c>
+      <c r="G262" s="6">
+        <v>46345</v>
+      </c>
+      <c r="H262" s="14"/>
+      <c r="I262" s="14"/>
+      <c r="J262" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A263" s="18">
+        <v>202610007000277</v>
+      </c>
+      <c r="B263" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C263" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D263" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E263" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F263" s="15">
+        <v>46317.376388888886</v>
+      </c>
+      <c r="G263" s="7">
+        <v>46347</v>
+      </c>
+      <c r="H263" s="14"/>
+      <c r="I263" s="14"/>
+      <c r="J263" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A264" s="17">
+        <v>202610012000278</v>
+      </c>
+      <c r="B264" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C264" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D264" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E264" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F264" s="13">
+        <v>46321.572222222225</v>
+      </c>
+      <c r="G264" s="6">
+        <v>46351</v>
+      </c>
+      <c r="H264" s="27"/>
+      <c r="I264" s="14"/>
+      <c r="J264" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A265" s="18">
+        <v>202610007000279</v>
+      </c>
+      <c r="B265" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C265" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D265" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E265" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F265" s="15">
+        <v>46323.581250000003</v>
+      </c>
+      <c r="G265" s="7">
+        <v>46353</v>
+      </c>
+      <c r="H265" s="14"/>
+      <c r="I265" s="14"/>
+      <c r="J265" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J247" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
+  <autoFilter ref="A1:J265" xr:uid="{46FC5506-0DB1-4429-ACA5-1B94AE29F551}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J159">
     <sortCondition ref="F1:F159"/>
   </sortState>
